--- a/docs/Decodifiche/143_dmnm_dec_filiazione.xlsx
+++ b/docs/Decodifiche/143_dmnm_dec_filiazione.xlsx
@@ -35,7 +35,7 @@
     <t>Nel matrimonio</t>
   </si>
   <si>
-    <t>2025-12-02 20:22:37.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
